--- a/test-exports/stock-movements-2020-01-01-to-2030-01-01.xlsx
+++ b/test-exports/stock-movements-2020-01-01-to-2030-01-01.xlsx
@@ -1256,36 +1256,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="KusumExport1" displayName="KusumExport1" ref="A6:J88" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A6:J88">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
-    <filterColumn colId="8" hiddenButton="1"/>
-    <filterColumn colId="9" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="10">
-    <tableColumn id="1" name="Movement date" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Movement type" totalsRowFunction="none"/>
-    <tableColumn id="3" name="Barcode" totalsRowFunction="none"/>
-    <tableColumn id="4" name="SKU" totalsRowFunction="none"/>
-    <tableColumn id="5" name="Item name" totalsRowFunction="none"/>
-    <tableColumn id="6" name="Metal" totalsRowFunction="none"/>
-    <tableColumn id="7" name="Purity" totalsRowFunction="none"/>
-    <tableColumn id="8" name="Qty change" totalsRowFunction="none"/>
-    <tableColumn id="9" name="Net wt. (g)" totalsRowFunction="none"/>
-    <tableColumn id="10" name="Note" totalsRowFunction="none"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4366,8 +4336,5 @@
     <oddFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</evenFooter>
   </headerFooter>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>